--- a/Test_case_DATN.xlsx
+++ b/Test_case_DATN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ĐATN\libpro_test_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51E1852-7E66-40DD-B813-8819660D329C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D637A4FA-6DA9-4221-AA9B-6F3C08F42DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="3" xr2:uid="{AD77D8C6-8764-47C1-A11F-044732BBF24F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{AD77D8C6-8764-47C1-A11F-044732BBF24F}"/>
   </bookViews>
   <sheets>
     <sheet name="Đăng nhập" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="222">
   <si>
     <t>Build Version</t>
   </si>
@@ -230,13 +230,6 @@
     <t>TC_QLS_005</t>
   </si>
   <si>
-    <t>Tên sách: Những Ngôi Sao Xa Xôi
-Tác giả: Lê Minh Khuê
-Thể loại: Văn học Việt Nam
-Số lượng: 2
-Nội dung tóm tắt: Những ngôi sao xa xôi" (1971) của Lê Minh Khuê là truyện ngắn xuất sắc về thế hệ trẻ thời kháng chiến chống Mỹ.</t>
-  </si>
-  <si>
     <t>Kiểm tra thêm mới sách khi nhập đầy đủ thông tin các trường</t>
   </si>
   <si>
@@ -574,11 +567,6 @@
     <t>Kiểm tra khi nhập thông tin mượn không hợp lệ</t>
   </si>
   <si>
-    <t>Ngày mượn: 15/04/2026
-Ngày trả: 20/04/2026
-Số lượng: 1</t>
-  </si>
-  <si>
     <t>1. Nhập đầy đủ thông tin mượn.
 2. Nhấn nút "Mượn ngay".</t>
   </si>
@@ -658,6 +646,88 @@
   <si>
     <t xml:space="preserve">username: anngo
 password: </t>
+  </si>
+  <si>
+    <t>TC_QLS_007</t>
+  </si>
+  <si>
+    <t>TC_QLS_002</t>
+  </si>
+  <si>
+    <t>Hiển thị popup nội dung quy định.</t>
+  </si>
+  <si>
+    <t>1. Kích vào biểu tượng "X".</t>
+  </si>
+  <si>
+    <t>Hiển thị danh sách trống</t>
+  </si>
+  <si>
+    <t>Hiển thị các sách đúng với tìm kiếm</t>
+  </si>
+  <si>
+    <t>1. Nhập thông tin hợp lệ vào tất cả các trường có dấu *
+2. Bỏ trống Ảnh bìa và các trường không có dấu *
+3.  Click nút "Lưu".</t>
+  </si>
+  <si>
+    <t>1. Để trống một hoặc nhiều trường có dấu * (VD: Tên sách, Số lượng)
+2.  Click nút "Lưu".</t>
+  </si>
+  <si>
+    <t>Hệ thống đóng form, hiển thị thông báo "Thêm sách thành công" và cập nhật đầu sách mới vào danh sách. Các trường bị bỏ trống sẽ hiển thị giá trị mặc định.</t>
+  </si>
+  <si>
+    <t>Skipped</t>
+  </si>
+  <si>
+    <t>Skipped: Bỏ qua case</t>
+  </si>
+  <si>
+    <t>Đăng nhập</t>
+  </si>
+  <si>
+    <t>Quản lý sách - Thêm mới sách</t>
+  </si>
+  <si>
+    <t>Quản lý sách - Chỉnh sửa sách</t>
+  </si>
+  <si>
+    <t>Quản lý sách - Xóa, tìm kiếm</t>
+  </si>
+  <si>
+    <t>Quản lý mượn, trả</t>
+  </si>
+  <si>
+    <t>Mượn sách</t>
+  </si>
+  <si>
+    <t>Test case</t>
+  </si>
+  <si>
+    <t>Tổng test case</t>
+  </si>
+  <si>
+    <t>Tổng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tỉ lệ passed </t>
+  </si>
+  <si>
+    <t>Số đỏ</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>Ngày mượn: 33/04/2026
+Ngày trả: 20/05/2026
+Số lượng: -10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Truy cập vào trang Đăng nhập
+2. Kích vào link Quên mật khẩu
+</t>
   </si>
   <si>
     <t>Tên sách: Những Ngôi Sao Xa Xôi
@@ -665,91 +735,29 @@
 Thể loại: Văn học Việt Nam
 Số lượng: 2
 Độ tuổi: 12+
-Nội dung tóm tắt: Những ngôi sao xa xôi" (1971) của Lê Minh Khuê là truyện ngắn xuất sắc về thế hệ trẻ thời kháng chiến chống Mỹ.
+Nội dung tóm tắt: Những ngôi sao xa xôi là truyện ngắn xuất sắc về thế hệ trẻ thời kháng chiến chống Mỹ.
 Có thể bạn chưa biết: "Những ngôi sao xa xôi" được đưa vào tuyển tập các truyện ngắn hay nhất thế giới.</t>
   </si>
   <si>
-    <t>TC_QLS_007</t>
-  </si>
-  <si>
-    <t>TC_QLS_002</t>
-  </si>
-  <si>
-    <t>Hiển thị popup nội dung quy định.</t>
-  </si>
-  <si>
-    <t>1. Kích vào biểu tượng "X".</t>
-  </si>
-  <si>
-    <t>Hiển thị danh sách trống</t>
-  </si>
-  <si>
-    <t>Hiển thị các sách đúng với tìm kiếm</t>
-  </si>
-  <si>
-    <t>1. Tải lên một "Ảnh bìa sách" hợp lệ.
-2. Nhập đầy đủ thông tin vào các trường bắt buộc.
-3. Nhập thông tin vào các trường tùy chọn.
-4. Click nút "Lưu".</t>
-  </si>
-  <si>
-    <t>1. Nhập thông tin hợp lệ vào tất cả các trường có dấu *
-2. Bỏ trống Ảnh bìa và các trường không có dấu *
-3.  Click nút "Lưu".</t>
-  </si>
-  <si>
-    <t>1. Để trống một hoặc nhiều trường có dấu * (VD: Tên sách, Số lượng)
+    <t>Tên sách: Những Ngôi Sao Xa Xôi
+Tác giả: Lê Minh Khuê
+Thể loại: Văn học Việt Nam
+Số lượng: 2
+Nội dung tóm tắt: Những ngôi sao xa xôi là truyện ngắn xuất sắc về thế hệ trẻ thời kháng chiến chống Mỹ.</t>
+  </si>
+  <si>
+    <t>1. Nhập chữ cái, ký tự đặc biệt hoặc số âm (VD: -5, abc) vào trường "Số lượng"
 2.  Click nút "Lưu".</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Nhập chữ cái, ký tự đặc biệt hoặc số âm (VD: -5, abc) vào trường "Số lượng"
-2.  Click nút "Lưu".
+    <t xml:space="preserve">1. Nhập đầy đủ thông tin vào các trường bắt buộc và tùy chọn.
+2. Click nút "Lưu".
 </t>
   </si>
   <si>
-    <t>Hệ thống đóng form, hiển thị thông báo "Thêm sách thành công" và cập nhật đầu sách mới vào danh sách. Các trường bị bỏ trống sẽ hiển thị giá trị mặc định.</t>
-  </si>
-  <si>
-    <t>Skipped</t>
-  </si>
-  <si>
-    <t>Skipped: Bỏ qua case</t>
-  </si>
-  <si>
-    <t>Đăng nhập</t>
-  </si>
-  <si>
-    <t>Quản lý sách - Thêm mới sách</t>
-  </si>
-  <si>
-    <t>Quản lý sách - Chỉnh sửa sách</t>
-  </si>
-  <si>
-    <t>Quản lý sách - Xóa, tìm kiếm</t>
-  </si>
-  <si>
-    <t>Quản lý mượn, trả</t>
-  </si>
-  <si>
-    <t>Mượn sách</t>
-  </si>
-  <si>
-    <t>Test case</t>
-  </si>
-  <si>
-    <t>Tổng test case</t>
-  </si>
-  <si>
-    <t>Tổng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tỉ lệ passed </t>
-  </si>
-  <si>
-    <t>Số đỏ</t>
-  </si>
-  <si>
-    <t>ABC</t>
+    <t>Ngày mượn: 15/04/2026
+Ngày trả: 20/04/2026
+Số lượng: 2</t>
   </si>
 </sst>
 </file>
@@ -2053,14 +2061,14 @@
     </row>
     <row r="7" spans="1:10" ht="16.2" thickBot="1">
       <c r="A7" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B7" s="13">
         <f>COUNTIF(H10:H237,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
@@ -2127,7 +2135,7 @@
         <v>23</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>38</v>
@@ -2153,7 +2161,7 @@
         <v>27</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>38</v>
@@ -2170,14 +2178,14 @@
     </row>
     <row r="12" spans="1:10" ht="76.2" customHeight="1" thickBot="1">
       <c r="A12" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>38</v>
@@ -2197,11 +2205,11 @@
         <v>30</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>38</v>
@@ -2225,7 +2233,7 @@
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>38</v>
@@ -2249,7 +2257,7 @@
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>38</v>
@@ -2273,7 +2281,7 @@
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>38</v>
@@ -2342,7 +2350,7 @@
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7" t="s">
-        <v>38</v>
+        <v>216</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>51</v>
@@ -2400,11 +2408,11 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="42.33203125" customWidth="1"/>
+    <col min="2" max="2" width="35.77734375" customWidth="1"/>
     <col min="3" max="3" width="34.88671875" customWidth="1"/>
     <col min="4" max="4" width="45.6640625" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
-    <col min="6" max="6" width="47.109375" customWidth="1"/>
+    <col min="6" max="6" width="37.109375" customWidth="1"/>
     <col min="7" max="7" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2507,14 +2515,14 @@
     </row>
     <row r="7" spans="1:10" ht="16.2" thickBot="1">
       <c r="A7" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B7" s="13">
         <f>COUNTIF(H10:H237,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
@@ -2570,22 +2578,22 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:10" ht="61.8" customHeight="1" thickBot="1">
+    <row r="10" spans="1:10" ht="44.4" customHeight="1" thickBot="1">
       <c r="A10" s="24" t="s">
         <v>53</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" s="25" t="s">
         <v>55</v>
       </c>
       <c r="D10" s="26"/>
       <c r="E10" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="25" t="s">
         <v>72</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>73</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>25</v>
@@ -2594,24 +2602,24 @@
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
     </row>
-    <row r="11" spans="1:10" ht="172.2" customHeight="1" thickBot="1">
+    <row r="11" spans="1:10" ht="147.6" customHeight="1" thickBot="1">
       <c r="A11" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>25</v>
@@ -2625,19 +2633,19 @@
         <v>56</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>59</v>
+        <v>218</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>25</v>
@@ -2646,22 +2654,22 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:10" ht="93" customHeight="1" thickBot="1">
+    <row r="13" spans="1:10" ht="57.6" customHeight="1" thickBot="1">
       <c r="A13" s="7" t="s">
         <v>57</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>25</v>
@@ -2670,24 +2678,24 @@
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
     </row>
-    <row r="14" spans="1:10" ht="109.2" customHeight="1" thickBot="1">
+    <row r="14" spans="1:10" ht="67.2" customHeight="1" thickBot="1">
       <c r="A14" s="7" t="s">
         <v>58</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>21</v>
@@ -2696,22 +2704,22 @@
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
     </row>
-    <row r="15" spans="1:10" ht="79.8" customHeight="1" thickBot="1">
+    <row r="15" spans="1:10" ht="49.2" customHeight="1" thickBot="1">
       <c r="A15" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>66</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>67</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>21</v>
@@ -2766,11 +2774,11 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.109375" customWidth="1"/>
-    <col min="2" max="2" width="35.109375" customWidth="1"/>
-    <col min="3" max="3" width="27.88671875" customWidth="1"/>
+    <col min="2" max="2" width="33.6640625" customWidth="1"/>
+    <col min="3" max="3" width="29.6640625" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="40.21875" customWidth="1"/>
-    <col min="6" max="6" width="36" customWidth="1"/>
+    <col min="6" max="6" width="37.77734375" customWidth="1"/>
     <col min="7" max="7" width="12.109375" style="23" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2873,14 +2881,14 @@
     </row>
     <row r="7" spans="1:10" ht="16.2" thickBot="1">
       <c r="A7" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B7" s="13">
         <f>COUNTIF(H10:H237,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
@@ -2936,22 +2944,22 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:10" ht="58.2" customHeight="1" thickBot="1">
+    <row r="10" spans="1:10" ht="43.8" customHeight="1" thickBot="1">
       <c r="A10" s="24" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C10" s="25" t="s">
         <v>55</v>
       </c>
       <c r="D10" s="26"/>
       <c r="E10" s="25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G10" s="27" t="s">
         <v>25</v>
@@ -2960,22 +2968,22 @@
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
     </row>
-    <row r="11" spans="1:10" ht="145.80000000000001" customHeight="1" thickBot="1">
+    <row r="11" spans="1:10" ht="90" customHeight="1" thickBot="1">
       <c r="A11" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D11" s="20"/>
       <c r="E11" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G11" s="22" t="s">
         <v>25</v>
@@ -2984,24 +2992,24 @@
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
     </row>
-    <row r="12" spans="1:10" ht="115.2" customHeight="1" thickBot="1">
+    <row r="12" spans="1:10" ht="99" customHeight="1" thickBot="1">
       <c r="A12" s="24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>59</v>
+        <v>218</v>
       </c>
       <c r="E12" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>85</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>86</v>
       </c>
       <c r="G12" s="22" t="s">
         <v>25</v>
@@ -3010,22 +3018,22 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:10" ht="82.8" customHeight="1" thickBot="1">
+    <row r="13" spans="1:10" ht="49.2" customHeight="1" thickBot="1">
       <c r="A13" s="24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>88</v>
       </c>
       <c r="G13" s="22" t="s">
         <v>25</v>
@@ -3034,22 +3042,22 @@
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
     </row>
-    <row r="14" spans="1:10" ht="66" customHeight="1" thickBot="1">
+    <row r="14" spans="1:10" ht="54.6" customHeight="1" thickBot="1">
       <c r="A14" s="24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>89</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>90</v>
       </c>
       <c r="G14" s="22" t="s">
         <v>21</v>
@@ -3058,22 +3066,22 @@
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
     </row>
-    <row r="15" spans="1:10" ht="61.8" customHeight="1" thickBot="1">
+    <row r="15" spans="1:10" ht="60" customHeight="1" thickBot="1">
       <c r="A15" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G15" s="22" t="s">
         <v>21</v>
@@ -3236,14 +3244,14 @@
     </row>
     <row r="7" spans="1:10" ht="16.2" thickBot="1">
       <c r="A7" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B7" s="13">
         <f>COUNTIF(H10:H237,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
@@ -3301,20 +3309,20 @@
     </row>
     <row r="10" spans="1:10" ht="34.799999999999997" customHeight="1" thickBot="1">
       <c r="A10" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>106</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>107</v>
       </c>
       <c r="G10" s="22" t="s">
         <v>25</v>
@@ -3325,20 +3333,20 @@
     </row>
     <row r="11" spans="1:10" ht="82.2" customHeight="1" thickBot="1">
       <c r="A11" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D11" s="20"/>
       <c r="E11" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>113</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>114</v>
       </c>
       <c r="G11" s="22" t="s">
         <v>25</v>
@@ -3349,20 +3357,20 @@
     </row>
     <row r="12" spans="1:10" ht="63" customHeight="1" thickBot="1">
       <c r="A12" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>116</v>
       </c>
       <c r="G12" s="22" t="s">
         <v>25</v>
@@ -3373,22 +3381,22 @@
     </row>
     <row r="13" spans="1:10" ht="60" customHeight="1" thickBot="1">
       <c r="A13" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G13" s="22" t="s">
         <v>21</v>
@@ -3399,22 +3407,22 @@
     </row>
     <row r="14" spans="1:10" ht="46.8" customHeight="1" thickBot="1">
       <c r="A14" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>54</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G14" s="22" t="s">
         <v>21</v>
@@ -3472,8 +3480,8 @@
     <col min="2" max="2" width="32.88671875" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
     <col min="4" max="4" width="21.21875" customWidth="1"/>
-    <col min="5" max="5" width="38" customWidth="1"/>
-    <col min="6" max="6" width="38.44140625" customWidth="1"/>
+    <col min="5" max="5" width="39.5546875" customWidth="1"/>
+    <col min="6" max="6" width="47.21875" customWidth="1"/>
     <col min="7" max="7" width="9.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3576,14 +3584,14 @@
     </row>
     <row r="7" spans="1:10" ht="16.2" thickBot="1">
       <c r="A7" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B7" s="13">
         <f>COUNTIF(H10:H237,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
@@ -3639,22 +3647,22 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:10" ht="56.4" customHeight="1" thickBot="1">
+    <row r="10" spans="1:10" ht="40.799999999999997" customHeight="1" thickBot="1">
       <c r="A10" s="24" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D10" s="26"/>
       <c r="E10" s="25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>25</v>
@@ -3663,22 +3671,22 @@
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
     </row>
-    <row r="11" spans="1:10" ht="67.8" customHeight="1" thickBot="1">
+    <row r="11" spans="1:10" ht="47.4" customHeight="1" thickBot="1">
       <c r="A11" s="24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D11" s="26"/>
       <c r="E11" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>25</v>
@@ -3687,22 +3695,22 @@
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
     </row>
-    <row r="12" spans="1:10" ht="58.8" customHeight="1" thickBot="1">
+    <row r="12" spans="1:10" ht="33.6" customHeight="1" thickBot="1">
       <c r="A12" s="24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D12" s="26"/>
       <c r="E12" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>25</v>
@@ -3711,22 +3719,22 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:10" ht="58.2" customHeight="1" thickBot="1">
+    <row r="13" spans="1:10" ht="37.799999999999997" customHeight="1" thickBot="1">
       <c r="A13" s="24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>25</v>
@@ -3737,20 +3745,20 @@
     </row>
     <row r="14" spans="1:10" ht="45.6" customHeight="1" thickBot="1">
       <c r="A14" s="24" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>21</v>
@@ -3759,22 +3767,22 @@
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
     </row>
-    <row r="15" spans="1:10" ht="40.799999999999997" customHeight="1" thickBot="1">
+    <row r="15" spans="1:10" ht="36.6" customHeight="1" thickBot="1">
       <c r="A15" s="24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>21</v>
@@ -3783,22 +3791,22 @@
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
     </row>
-    <row r="16" spans="1:10" ht="62.4" customHeight="1" thickBot="1">
+    <row r="16" spans="1:10" ht="44.4" customHeight="1" thickBot="1">
       <c r="A16" s="24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>21</v>
@@ -3807,22 +3815,22 @@
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
     </row>
-    <row r="17" spans="1:10" ht="73.8" customHeight="1" thickBot="1">
+    <row r="17" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A17" s="24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>21</v>
@@ -3831,22 +3839,22 @@
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
     </row>
-    <row r="18" spans="1:10" ht="58.8" customHeight="1" thickBot="1">
+    <row r="18" spans="1:10" ht="36.6" customHeight="1" thickBot="1">
       <c r="A18" s="24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>21</v>
@@ -3904,8 +3912,8 @@
     <col min="2" max="2" width="31.5546875" customWidth="1"/>
     <col min="3" max="3" width="27.6640625" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="37" customWidth="1"/>
-    <col min="6" max="6" width="31.21875" customWidth="1"/>
+    <col min="5" max="5" width="38.77734375" customWidth="1"/>
+    <col min="6" max="6" width="33.44140625" customWidth="1"/>
     <col min="7" max="7" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4008,14 +4016,14 @@
     </row>
     <row r="7" spans="1:10" ht="16.2" thickBot="1">
       <c r="A7" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B7" s="13">
         <f>COUNTIF(H10:H237,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
@@ -4071,24 +4079,24 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:10" ht="54.6" customHeight="1" thickBot="1">
+    <row r="10" spans="1:10" ht="46.8" customHeight="1" thickBot="1">
       <c r="A10" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D10" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" s="25" t="s">
         <v>169</v>
-      </c>
-      <c r="E10" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>171</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>25</v>
@@ -4097,22 +4105,24 @@
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
     </row>
-    <row r="11" spans="1:10" ht="55.2" customHeight="1" thickBot="1">
+    <row r="11" spans="1:10" ht="43.8" customHeight="1" thickBot="1">
       <c r="A11" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="D11" s="26"/>
+        <v>166</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>215</v>
+      </c>
       <c r="E11" s="25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>25</v>
@@ -4121,22 +4131,22 @@
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
     </row>
-    <row r="12" spans="1:10" ht="56.4" customHeight="1" thickBot="1">
+    <row r="12" spans="1:10" ht="43.8" customHeight="1" thickBot="1">
       <c r="A12" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="25" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>25</v>
@@ -4145,22 +4155,22 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:10" ht="65.400000000000006" customHeight="1" thickBot="1">
+    <row r="13" spans="1:10" ht="42" customHeight="1" thickBot="1">
       <c r="A13" s="24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>21</v>
@@ -4171,20 +4181,20 @@
     </row>
     <row r="14" spans="1:10" ht="65.400000000000006" customHeight="1" thickBot="1">
       <c r="A14" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>176</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>178</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>21</v>
@@ -4195,20 +4205,20 @@
     </row>
     <row r="15" spans="1:10" ht="47.4" customHeight="1" thickBot="1">
       <c r="A15" s="24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>175</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>177</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>21</v>
@@ -4217,22 +4227,22 @@
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
     </row>
-    <row r="16" spans="1:10" ht="52.8" customHeight="1" thickBot="1">
+    <row r="16" spans="1:10" ht="39" customHeight="1" thickBot="1">
       <c r="A16" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>21</v>
@@ -4241,22 +4251,22 @@
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
     </row>
-    <row r="17" spans="1:10" ht="55.2" customHeight="1" thickBot="1">
+    <row r="17" spans="1:10" ht="45.6" customHeight="1" thickBot="1">
       <c r="A17" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>21</v>
@@ -4318,10 +4328,10 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22.2" customHeight="1">
       <c r="A1" s="37" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C1" s="37" t="s">
         <v>5</v>
@@ -4330,15 +4340,15 @@
         <v>7</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="40" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B2" s="38">
         <f>COUNTIF('Đăng nhập'!A:A, "TC_*")</f>
@@ -4363,7 +4373,7 @@
     </row>
     <row r="3" spans="1:8" ht="31.2">
       <c r="A3" s="40" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B3" s="38">
         <f>COUNTIF('Quản lý sách - Thêm mới sách'!A:A, "TC_*")</f>
@@ -4388,7 +4398,7 @@
     </row>
     <row r="4" spans="1:8" ht="35.4" customHeight="1">
       <c r="A4" s="40" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B4" s="38">
         <f>COUNTIF('Quản lý sách - Chỉnh sửa sách'!A:A, "TC_*")</f>
@@ -4413,7 +4423,7 @@
     </row>
     <row r="5" spans="1:8" ht="31.2">
       <c r="A5" s="40" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B5" s="38">
         <f>COUNTIF('Quản lý sách - Xóa, tìm kiếm '!A:A, "TC_*")</f>
@@ -4438,7 +4448,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="40" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B6" s="38">
         <f>COUNTIF('Quản lý mượn, trả'!A:A, "TC_*")</f>
@@ -4463,7 +4473,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="40" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B7" s="38">
         <f>COUNTIF('Mượn sách'!A:A, "TC_*")</f>
@@ -4488,7 +4498,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="41" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B8" s="38">
         <f>SUM(B2:B7)</f>

--- a/Test_case_DATN.xlsx
+++ b/Test_case_DATN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ĐATN\libpro_test_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D637A4FA-6DA9-4221-AA9B-6F3C08F42DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F602FE-63DA-41A4-A392-9B8A10FE7061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{AD77D8C6-8764-47C1-A11F-044732BBF24F}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="222">
   <si>
     <t>Build Version</t>
   </si>
@@ -1951,7 +1951,7 @@
   <cols>
     <col min="1" max="1" width="17.77734375" customWidth="1"/>
     <col min="2" max="2" width="39.5546875" customWidth="1"/>
-    <col min="3" max="3" width="34.109375" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" customWidth="1"/>
     <col min="4" max="4" width="22.77734375" customWidth="1"/>
     <col min="5" max="5" width="39.33203125" customWidth="1"/>
     <col min="6" max="6" width="48.6640625" customWidth="1"/>
@@ -2409,7 +2409,7 @@
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
     <col min="2" max="2" width="35.77734375" customWidth="1"/>
-    <col min="3" max="3" width="34.88671875" customWidth="1"/>
+    <col min="3" max="3" width="39" customWidth="1"/>
     <col min="4" max="4" width="45.6640625" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="37.109375" customWidth="1"/>
@@ -3478,7 +3478,7 @@
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
     <col min="2" max="2" width="32.88671875" customWidth="1"/>
-    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="3" max="3" width="32.5546875" customWidth="1"/>
     <col min="4" max="4" width="21.21875" customWidth="1"/>
     <col min="5" max="5" width="39.5546875" customWidth="1"/>
     <col min="6" max="6" width="47.21875" customWidth="1"/>
@@ -3910,7 +3910,7 @@
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="31.5546875" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="38.77734375" customWidth="1"/>
     <col min="6" max="6" width="33.44140625" customWidth="1"/>
@@ -4141,7 +4141,9 @@
       <c r="C12" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="D12" s="7"/>
+      <c r="D12" s="26" t="s">
+        <v>221</v>
+      </c>
       <c r="E12" s="25" t="s">
         <v>168</v>
       </c>

--- a/Test_case_DATN.xlsx
+++ b/Test_case_DATN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ĐATN\libpro_test_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F602FE-63DA-41A4-A392-9B8A10FE7061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F478A96-5D47-4EFA-B15D-97B82A97D894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{AD77D8C6-8764-47C1-A11F-044732BBF24F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{AD77D8C6-8764-47C1-A11F-044732BBF24F}"/>
   </bookViews>
   <sheets>
     <sheet name="Đăng nhập" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="223">
   <si>
     <t>Build Version</t>
   </si>
@@ -327,9 +327,6 @@
 2. Nhấn “Cập nhật”</t>
   </si>
   <si>
-    <t>Hệ thống cảnh báo nhập dữ liệu hợp lệ,</t>
-  </si>
-  <si>
     <t>1. Click nút "Hủy"</t>
   </si>
   <si>
@@ -478,9 +475,6 @@
   </si>
   <si>
     <t>Hệ thống hiển thị popup xác nhận thu hồi sách.</t>
-  </si>
-  <si>
-    <t>Đóng popup, thông báo đã thu hồi sách, phần thao tác hiện. nút “Xóa”.</t>
   </si>
   <si>
     <t>Đóng popup và vẫn enable nút “Thu”.</t>
@@ -758,6 +752,15 @@
     <t>Ngày mượn: 15/04/2026
 Ngày trả: 20/04/2026
 Số lượng: 2</t>
+  </si>
+  <si>
+    <t>1. Nhấn link nội quy thư viện</t>
+  </si>
+  <si>
+    <t>Hệ thống cảnh báo nhập dữ liệu hợp lệ.</t>
+  </si>
+  <si>
+    <t>Đóng popup, thông báo đã thu hồi sách, phần thao tác hiện nút “Xóa”.</t>
   </si>
 </sst>
 </file>
@@ -2061,14 +2064,14 @@
     </row>
     <row r="7" spans="1:10" ht="16.2" thickBot="1">
       <c r="A7" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B7" s="13">
         <f>COUNTIF(H10:H237,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
@@ -2135,7 +2138,7 @@
         <v>23</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>38</v>
@@ -2161,7 +2164,7 @@
         <v>27</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>38</v>
@@ -2178,14 +2181,14 @@
     </row>
     <row r="12" spans="1:10" ht="76.2" customHeight="1" thickBot="1">
       <c r="A12" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>38</v>
@@ -2205,11 +2208,11 @@
         <v>30</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>38</v>
@@ -2233,7 +2236,7 @@
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>38</v>
@@ -2257,7 +2260,7 @@
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>38</v>
@@ -2281,7 +2284,7 @@
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>38</v>
@@ -2350,7 +2353,7 @@
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>51</v>
@@ -2515,14 +2518,14 @@
     </row>
     <row r="7" spans="1:10" ht="16.2" thickBot="1">
       <c r="A7" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B7" s="13">
         <f>COUNTIF(H10:H237,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
@@ -2604,19 +2607,19 @@
     </row>
     <row r="11" spans="1:10" ht="147.6" customHeight="1" thickBot="1">
       <c r="A11" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>59</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>69</v>
@@ -2636,16 +2639,16 @@
         <v>60</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E12" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>198</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>200</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>25</v>
@@ -2662,11 +2665,11 @@
         <v>61</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>68</v>
@@ -2686,13 +2689,13 @@
         <v>62</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>73</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>67</v>
@@ -2712,7 +2715,7 @@
         <v>63</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7" t="s">
@@ -2881,14 +2884,14 @@
     </row>
     <row r="7" spans="1:10" ht="16.2" thickBot="1">
       <c r="A7" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B7" s="13">
         <f>COUNTIF(H10:H237,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
@@ -2946,7 +2949,7 @@
     </row>
     <row r="10" spans="1:10" ht="43.8" customHeight="1" thickBot="1">
       <c r="A10" s="24" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>74</v>
@@ -2970,13 +2973,13 @@
     </row>
     <row r="11" spans="1:10" ht="90" customHeight="1" thickBot="1">
       <c r="A11" s="24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D11" s="20"/>
       <c r="E11" s="7" t="s">
@@ -2994,16 +2997,16 @@
     </row>
     <row r="12" spans="1:10" ht="99" customHeight="1" thickBot="1">
       <c r="A12" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>76</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>84</v>
@@ -3020,13 +3023,13 @@
     </row>
     <row r="13" spans="1:10" ht="49.2" customHeight="1" thickBot="1">
       <c r="A13" s="24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>77</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7" t="s">
@@ -3044,20 +3047,20 @@
     </row>
     <row r="14" spans="1:10" ht="54.6" customHeight="1" thickBot="1">
       <c r="A14" s="24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>78</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7" t="s">
         <v>88</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>89</v>
+        <v>221</v>
       </c>
       <c r="G14" s="22" t="s">
         <v>21</v>
@@ -3068,17 +3071,17 @@
     </row>
     <row r="15" spans="1:10" ht="60" customHeight="1" thickBot="1">
       <c r="A15" s="24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>79</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>66</v>
@@ -3244,14 +3247,14 @@
     </row>
     <row r="7" spans="1:10" ht="16.2" thickBot="1">
       <c r="A7" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B7" s="13">
         <f>COUNTIF(H10:H237,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
@@ -3309,20 +3312,20 @@
     </row>
     <row r="10" spans="1:10" ht="34.799999999999997" customHeight="1" thickBot="1">
       <c r="A10" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>105</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>106</v>
       </c>
       <c r="G10" s="22" t="s">
         <v>25</v>
@@ -3333,20 +3336,20 @@
     </row>
     <row r="11" spans="1:10" ht="82.2" customHeight="1" thickBot="1">
       <c r="A11" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D11" s="20"/>
       <c r="E11" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>112</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>113</v>
       </c>
       <c r="G11" s="22" t="s">
         <v>25</v>
@@ -3357,20 +3360,20 @@
     </row>
     <row r="12" spans="1:10" ht="63" customHeight="1" thickBot="1">
       <c r="A12" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>114</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>115</v>
       </c>
       <c r="G12" s="22" t="s">
         <v>25</v>
@@ -3381,22 +3384,22 @@
     </row>
     <row r="13" spans="1:10" ht="60" customHeight="1" thickBot="1">
       <c r="A13" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G13" s="22" t="s">
         <v>21</v>
@@ -3407,22 +3410,22 @@
     </row>
     <row r="14" spans="1:10" ht="46.8" customHeight="1" thickBot="1">
       <c r="A14" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>54</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G14" s="22" t="s">
         <v>21</v>
@@ -3584,14 +3587,14 @@
     </row>
     <row r="7" spans="1:10" ht="16.2" thickBot="1">
       <c r="A7" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B7" s="13">
         <f>COUNTIF(H10:H237,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
@@ -3649,20 +3652,20 @@
     </row>
     <row r="10" spans="1:10" ht="40.799999999999997" customHeight="1" thickBot="1">
       <c r="A10" s="24" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D10" s="26"/>
       <c r="E10" s="25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>25</v>
@@ -3673,20 +3676,20 @@
     </row>
     <row r="11" spans="1:10" ht="47.4" customHeight="1" thickBot="1">
       <c r="A11" s="24" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D11" s="26"/>
       <c r="E11" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>25</v>
@@ -3697,20 +3700,20 @@
     </row>
     <row r="12" spans="1:10" ht="33.6" customHeight="1" thickBot="1">
       <c r="A12" s="24" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D12" s="26"/>
       <c r="E12" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>25</v>
@@ -3721,20 +3724,20 @@
     </row>
     <row r="13" spans="1:10" ht="37.799999999999997" customHeight="1" thickBot="1">
       <c r="A13" s="24" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>25</v>
@@ -3745,20 +3748,20 @@
     </row>
     <row r="14" spans="1:10" ht="45.6" customHeight="1" thickBot="1">
       <c r="A14" s="24" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>21</v>
@@ -3769,20 +3772,20 @@
     </row>
     <row r="15" spans="1:10" ht="36.6" customHeight="1" thickBot="1">
       <c r="A15" s="24" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>21</v>
@@ -3793,20 +3796,20 @@
     </row>
     <row r="16" spans="1:10" ht="44.4" customHeight="1" thickBot="1">
       <c r="A16" s="24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>21</v>
@@ -3817,20 +3820,20 @@
     </row>
     <row r="17" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A17" s="24" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>21</v>
@@ -3841,20 +3844,20 @@
     </row>
     <row r="18" spans="1:10" ht="36.6" customHeight="1" thickBot="1">
       <c r="A18" s="24" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>21</v>
@@ -3910,7 +3913,7 @@
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="31.5546875" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="38.77734375" customWidth="1"/>
     <col min="6" max="6" width="33.44140625" customWidth="1"/>
@@ -4016,14 +4019,14 @@
     </row>
     <row r="7" spans="1:10" ht="16.2" thickBot="1">
       <c r="A7" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B7" s="13">
         <f>COUNTIF(H10:H237,"Skipped")</f>
         <v>0</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
@@ -4081,22 +4084,22 @@
     </row>
     <row r="10" spans="1:10" ht="46.8" customHeight="1" thickBot="1">
       <c r="A10" s="24" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C10" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="E10" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="D10" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="E10" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="F10" s="25" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G10" s="25" t="s">
         <v>25</v>
@@ -4107,22 +4110,22 @@
     </row>
     <row r="11" spans="1:10" ht="43.8" customHeight="1" thickBot="1">
       <c r="A11" s="24" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>25</v>
@@ -4133,22 +4136,22 @@
     </row>
     <row r="12" spans="1:10" ht="43.8" customHeight="1" thickBot="1">
       <c r="A12" s="24" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C12" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="E12" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="D12" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="F12" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>25</v>
@@ -4159,20 +4162,20 @@
     </row>
     <row r="13" spans="1:10" ht="42" customHeight="1" thickBot="1">
       <c r="A13" s="24" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>21</v>
@@ -4183,20 +4186,20 @@
     </row>
     <row r="14" spans="1:10" ht="65.400000000000006" customHeight="1" thickBot="1">
       <c r="A14" s="24" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>174</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>176</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>21</v>
@@ -4207,20 +4210,20 @@
     </row>
     <row r="15" spans="1:10" ht="47.4" customHeight="1" thickBot="1">
       <c r="A15" s="24" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>173</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>175</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>21</v>
@@ -4231,20 +4234,20 @@
     </row>
     <row r="16" spans="1:10" ht="39" customHeight="1" thickBot="1">
       <c r="A16" s="24" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>21</v>
@@ -4255,20 +4258,20 @@
     </row>
     <row r="17" spans="1:10" ht="45.6" customHeight="1" thickBot="1">
       <c r="A17" s="24" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="7" t="s">
-        <v>133</v>
+        <v>220</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>21</v>
@@ -4330,10 +4333,10 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22.2" customHeight="1">
       <c r="A1" s="37" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C1" s="37" t="s">
         <v>5</v>
@@ -4342,15 +4345,15 @@
         <v>7</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="40" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B2" s="38">
         <f>COUNTIF('Đăng nhập'!A:A, "TC_*")</f>
@@ -4375,7 +4378,7 @@
     </row>
     <row r="3" spans="1:8" ht="31.2">
       <c r="A3" s="40" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B3" s="38">
         <f>COUNTIF('Quản lý sách - Thêm mới sách'!A:A, "TC_*")</f>
@@ -4400,7 +4403,7 @@
     </row>
     <row r="4" spans="1:8" ht="35.4" customHeight="1">
       <c r="A4" s="40" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B4" s="38">
         <f>COUNTIF('Quản lý sách - Chỉnh sửa sách'!A:A, "TC_*")</f>
@@ -4425,7 +4428,7 @@
     </row>
     <row r="5" spans="1:8" ht="31.2">
       <c r="A5" s="40" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B5" s="38">
         <f>COUNTIF('Quản lý sách - Xóa, tìm kiếm '!A:A, "TC_*")</f>
@@ -4450,7 +4453,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="40" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B6" s="38">
         <f>COUNTIF('Quản lý mượn, trả'!A:A, "TC_*")</f>
@@ -4475,7 +4478,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="40" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B7" s="38">
         <f>COUNTIF('Mượn sách'!A:A, "TC_*")</f>
@@ -4500,7 +4503,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="41" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B8" s="38">
         <f>SUM(B2:B7)</f>
